--- a/research/traditional_assets/database/data/portugal/portugal_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_telecom_wireless.xlsx
@@ -588,118 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.007189999999999999</v>
+        <v>-0.109</v>
       </c>
       <c r="E2">
-        <v>2.148</v>
+        <v>0.152</v>
       </c>
       <c r="G2">
-        <v>-0.07488673139158576</v>
+        <v>-0.1323759791122716</v>
       </c>
       <c r="H2">
-        <v>-0.08802588996763754</v>
+        <v>-0.1514360313315927</v>
       </c>
       <c r="I2">
-        <v>-0.1029126213592233</v>
+        <v>-0.1605744125326371</v>
       </c>
       <c r="J2">
-        <v>-0.0987286627052035</v>
+        <v>-0.1405827912652582</v>
       </c>
       <c r="K2">
-        <v>115.1</v>
+        <v>133.5</v>
       </c>
       <c r="L2">
-        <v>0.7449838187702265</v>
+        <v>1.742819843342037</v>
       </c>
       <c r="M2">
-        <v>41.35</v>
+        <v>58.2</v>
       </c>
       <c r="N2">
-        <v>0.07057518347840928</v>
+        <v>0.07095830285296269</v>
       </c>
       <c r="O2">
-        <v>0.3592528236316247</v>
+        <v>0.4359550561797753</v>
       </c>
       <c r="P2">
-        <v>34.4</v>
+        <v>58.2</v>
       </c>
       <c r="Q2">
-        <v>0.05871309097115548</v>
+        <v>0.07095830285296269</v>
       </c>
       <c r="R2">
-        <v>0.2988705473501303</v>
+        <v>0.4359550561797753</v>
       </c>
       <c r="S2">
-        <v>6.950000000000003</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1680773881499396</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>258.2</v>
+        <v>226.1</v>
       </c>
       <c r="V2">
-        <v>0.440689537463731</v>
+        <v>0.2756644720799805</v>
       </c>
       <c r="W2">
-        <v>0.09140724269377382</v>
+        <v>0.1009146571925316</v>
       </c>
       <c r="X2">
-        <v>0.05853765914958723</v>
+        <v>0.09466292836141046</v>
       </c>
       <c r="Y2">
-        <v>0.03286958354418659</v>
+        <v>0.006251728831121087</v>
       </c>
       <c r="Z2">
-        <v>0.1563923474035834</v>
+        <v>0.071662456731219</v>
       </c>
       <c r="AA2">
-        <v>-0.01544040731648339</v>
+        <v>-0.01007450819620056</v>
       </c>
       <c r="AB2">
-        <v>0.0575930612543887</v>
+        <v>0.0943501409844496</v>
       </c>
       <c r="AC2">
-        <v>-0.07303346857087209</v>
+        <v>-0.1044246491806502</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>6.65</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21</v>
+        <v>6.65</v>
       </c>
       <c r="AG2">
-        <v>-237.2</v>
+        <v>-219.45</v>
       </c>
       <c r="AH2">
-        <v>0.03460207612456748</v>
+        <v>0.008042571203966863</v>
       </c>
       <c r="AI2">
-        <v>0.0154753131908622</v>
+        <v>0.005437226605617104</v>
       </c>
       <c r="AJ2">
-        <v>-0.6802408947519357</v>
+        <v>-0.3652933832709113</v>
       </c>
       <c r="AK2">
-        <v>-0.2158718602111394</v>
+        <v>-0.2201213701790461</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="AM2">
-        <v>-1.08</v>
+        <v>-2.827</v>
       </c>
       <c r="AN2">
-        <v>-1.48936170212766</v>
+        <v>-0.6785714285714286</v>
+      </c>
+      <c r="AO2">
+        <v>-31.29770992366412</v>
       </c>
       <c r="AP2">
-        <v>16.82269503546099</v>
+        <v>22.39285714285714</v>
       </c>
       <c r="AQ2">
-        <v>14.72222222222222</v>
+        <v>4.350902016271666</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.007189999999999999</v>
+        <v>-0.109</v>
       </c>
       <c r="E3">
-        <v>2.148</v>
+        <v>0.152</v>
       </c>
       <c r="G3">
-        <v>-0.07488673139158576</v>
+        <v>-0.1323759791122716</v>
       </c>
       <c r="H3">
-        <v>-0.08802588996763754</v>
+        <v>-0.1514360313315927</v>
       </c>
       <c r="I3">
-        <v>-0.1029126213592233</v>
+        <v>-0.1605744125326371</v>
       </c>
       <c r="J3">
-        <v>-0.0987286627052035</v>
+        <v>-0.1405827912652582</v>
       </c>
       <c r="K3">
-        <v>115.1</v>
+        <v>133.5</v>
       </c>
       <c r="L3">
-        <v>0.7449838187702265</v>
+        <v>1.742819843342037</v>
       </c>
       <c r="M3">
-        <v>41.35</v>
+        <v>58.2</v>
       </c>
       <c r="N3">
-        <v>0.07057518347840928</v>
+        <v>0.07095830285296269</v>
       </c>
       <c r="O3">
-        <v>0.3592528236316247</v>
+        <v>0.4359550561797753</v>
       </c>
       <c r="P3">
-        <v>34.4</v>
+        <v>58.2</v>
       </c>
       <c r="Q3">
-        <v>0.05871309097115548</v>
+        <v>0.07095830285296269</v>
       </c>
       <c r="R3">
-        <v>0.2988705473501303</v>
+        <v>0.4359550561797753</v>
       </c>
       <c r="S3">
-        <v>6.950000000000003</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.1680773881499396</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>258.2</v>
+        <v>226.1</v>
       </c>
       <c r="V3">
-        <v>0.440689537463731</v>
+        <v>0.2756644720799805</v>
       </c>
       <c r="W3">
-        <v>0.09140724269377382</v>
+        <v>0.1009146571925316</v>
       </c>
       <c r="X3">
-        <v>0.05853765914958723</v>
+        <v>0.09466292836141046</v>
       </c>
       <c r="Y3">
-        <v>0.03286958354418659</v>
+        <v>0.006251728831121087</v>
       </c>
       <c r="Z3">
-        <v>0.1563923474035834</v>
+        <v>0.071662456731219</v>
       </c>
       <c r="AA3">
-        <v>-0.01544040731648339</v>
+        <v>-0.01007450819620056</v>
       </c>
       <c r="AB3">
-        <v>0.0575930612543887</v>
+        <v>0.0943501409844496</v>
       </c>
       <c r="AC3">
-        <v>-0.07303346857087209</v>
+        <v>-0.1044246491806502</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>6.65</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>6.65</v>
       </c>
       <c r="AG3">
-        <v>-237.2</v>
+        <v>-219.45</v>
       </c>
       <c r="AH3">
-        <v>0.03460207612456748</v>
+        <v>0.008042571203966863</v>
       </c>
       <c r="AI3">
-        <v>0.0154753131908622</v>
+        <v>0.005437226605617104</v>
       </c>
       <c r="AJ3">
-        <v>-0.6802408947519357</v>
+        <v>-0.3652933832709113</v>
       </c>
       <c r="AK3">
-        <v>-0.2158718602111394</v>
+        <v>-0.2201213701790461</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="AM3">
-        <v>-1.08</v>
+        <v>-2.827</v>
       </c>
       <c r="AN3">
-        <v>-1.48936170212766</v>
+        <v>-0.6785714285714286</v>
+      </c>
+      <c r="AO3">
+        <v>-31.29770992366412</v>
       </c>
       <c r="AP3">
-        <v>16.82269503546099</v>
+        <v>22.39285714285714</v>
       </c>
       <c r="AQ3">
-        <v>14.72222222222222</v>
+        <v>4.350902016271666</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/portugal/portugal_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_telecom_wireless.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.109</v>
+        <v>-0.293</v>
       </c>
       <c r="E2">
-        <v>0.152</v>
+        <v>0.112</v>
       </c>
       <c r="G2">
-        <v>-0.1323759791122716</v>
+        <v>-0.4799061032863849</v>
       </c>
       <c r="H2">
-        <v>-0.1514360313315927</v>
+        <v>-0.5164319248826291</v>
       </c>
       <c r="I2">
-        <v>-0.1605744125326371</v>
+        <v>-0.5915492957746479</v>
       </c>
       <c r="J2">
-        <v>-0.1405827912652582</v>
+        <v>-0.5915492957746479</v>
       </c>
       <c r="K2">
-        <v>133.5</v>
+        <v>100.3</v>
       </c>
       <c r="L2">
-        <v>1.742819843342037</v>
+        <v>4.708920187793427</v>
       </c>
       <c r="M2">
-        <v>58.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N2">
-        <v>0.07095830285296269</v>
+        <v>0.01026101659093311</v>
       </c>
       <c r="O2">
-        <v>0.4359550561797753</v>
+        <v>0.09680957128614158</v>
       </c>
       <c r="P2">
-        <v>58.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.07095830285296269</v>
+        <v>0.01026101659093311</v>
       </c>
       <c r="R2">
-        <v>0.4359550561797753</v>
+        <v>0.09680957128614158</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>226.1</v>
+        <v>173.7</v>
       </c>
       <c r="V2">
-        <v>0.2756644720799805</v>
+        <v>0.1835570115185459</v>
       </c>
       <c r="W2">
-        <v>0.1009146571925316</v>
+        <v>0.08294054411643099</v>
       </c>
       <c r="X2">
-        <v>0.09466292836141046</v>
+        <v>0.07943599718741132</v>
       </c>
       <c r="Y2">
-        <v>0.006251728831121087</v>
+        <v>0.003504546929019678</v>
       </c>
       <c r="Z2">
-        <v>0.071662456731219</v>
+        <v>0.02154322298752921</v>
       </c>
       <c r="AA2">
-        <v>-0.01007450819620056</v>
+        <v>-0.01274387838698911</v>
       </c>
       <c r="AB2">
-        <v>0.0943501409844496</v>
+        <v>0.07921317047985563</v>
       </c>
       <c r="AC2">
-        <v>-0.1044246491806502</v>
+        <v>-0.09195704886684473</v>
       </c>
       <c r="AD2">
-        <v>6.65</v>
+        <v>6.33</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.65</v>
+        <v>6.33</v>
       </c>
       <c r="AG2">
-        <v>-219.45</v>
+        <v>-167.37</v>
       </c>
       <c r="AH2">
-        <v>0.008042571203966863</v>
+        <v>0.006644762394633803</v>
       </c>
       <c r="AI2">
-        <v>0.005437226605617104</v>
+        <v>0.004501397353206801</v>
       </c>
       <c r="AJ2">
-        <v>-0.3652933832709113</v>
+        <v>-0.2148716829496874</v>
       </c>
       <c r="AK2">
-        <v>-0.2201213701790461</v>
+        <v>-0.1357938549163103</v>
       </c>
       <c r="AL2">
-        <v>0.393</v>
+        <v>0.13</v>
       </c>
       <c r="AM2">
-        <v>-2.827</v>
+        <v>-5.32</v>
       </c>
       <c r="AN2">
-        <v>-0.6785714285714286</v>
+        <v>-0.5231404958677686</v>
       </c>
       <c r="AO2">
-        <v>-31.29770992366412</v>
+        <v>-96.92307692307692</v>
       </c>
       <c r="AP2">
-        <v>22.39285714285714</v>
+        <v>13.83223140495868</v>
       </c>
       <c r="AQ2">
-        <v>4.350902016271666</v>
+        <v>2.368421052631579</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.109</v>
+        <v>-0.293</v>
       </c>
       <c r="E3">
-        <v>0.152</v>
+        <v>0.112</v>
       </c>
       <c r="G3">
-        <v>-0.1323759791122716</v>
+        <v>-0.4799061032863849</v>
       </c>
       <c r="H3">
-        <v>-0.1514360313315927</v>
+        <v>-0.5164319248826291</v>
       </c>
       <c r="I3">
-        <v>-0.1605744125326371</v>
+        <v>-0.5915492957746479</v>
       </c>
       <c r="J3">
-        <v>-0.1405827912652582</v>
+        <v>-0.5915492957746479</v>
       </c>
       <c r="K3">
-        <v>133.5</v>
+        <v>100.3</v>
       </c>
       <c r="L3">
-        <v>1.742819843342037</v>
+        <v>4.708920187793427</v>
       </c>
       <c r="M3">
-        <v>58.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N3">
-        <v>0.07095830285296269</v>
+        <v>0.01026101659093311</v>
       </c>
       <c r="O3">
-        <v>0.4359550561797753</v>
+        <v>0.09680957128614158</v>
       </c>
       <c r="P3">
-        <v>58.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.07095830285296269</v>
+        <v>0.01026101659093311</v>
       </c>
       <c r="R3">
-        <v>0.4359550561797753</v>
+        <v>0.09680957128614158</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>226.1</v>
+        <v>173.7</v>
       </c>
       <c r="V3">
-        <v>0.2756644720799805</v>
+        <v>0.1835570115185459</v>
       </c>
       <c r="W3">
-        <v>0.1009146571925316</v>
+        <v>0.08294054411643099</v>
       </c>
       <c r="X3">
-        <v>0.09466292836141046</v>
+        <v>0.07943599718741132</v>
       </c>
       <c r="Y3">
-        <v>0.006251728831121087</v>
+        <v>0.003504546929019678</v>
       </c>
       <c r="Z3">
-        <v>0.071662456731219</v>
+        <v>0.02154322298752921</v>
       </c>
       <c r="AA3">
-        <v>-0.01007450819620056</v>
+        <v>-0.01274387838698911</v>
       </c>
       <c r="AB3">
-        <v>0.0943501409844496</v>
+        <v>0.07921317047985563</v>
       </c>
       <c r="AC3">
-        <v>-0.1044246491806502</v>
+        <v>-0.09195704886684473</v>
       </c>
       <c r="AD3">
-        <v>6.65</v>
+        <v>6.33</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.65</v>
+        <v>6.33</v>
       </c>
       <c r="AG3">
-        <v>-219.45</v>
+        <v>-167.37</v>
       </c>
       <c r="AH3">
-        <v>0.008042571203966863</v>
+        <v>0.006644762394633803</v>
       </c>
       <c r="AI3">
-        <v>0.005437226605617104</v>
+        <v>0.004501397353206801</v>
       </c>
       <c r="AJ3">
-        <v>-0.3652933832709113</v>
+        <v>-0.2148716829496874</v>
       </c>
       <c r="AK3">
-        <v>-0.2201213701790461</v>
+        <v>-0.1357938549163103</v>
       </c>
       <c r="AL3">
-        <v>0.393</v>
+        <v>0.13</v>
       </c>
       <c r="AM3">
-        <v>-2.827</v>
+        <v>-5.32</v>
       </c>
       <c r="AN3">
-        <v>-0.6785714285714286</v>
+        <v>-0.5231404958677686</v>
       </c>
       <c r="AO3">
-        <v>-31.29770992366412</v>
+        <v>-96.92307692307692</v>
       </c>
       <c r="AP3">
-        <v>22.39285714285714</v>
+        <v>13.83223140495868</v>
       </c>
       <c r="AQ3">
-        <v>4.350902016271666</v>
+        <v>2.368421052631579</v>
       </c>
     </row>
   </sheetData>
